--- a/public/plantilla-residuos.xlsx
+++ b/public/plantilla-residuos.xlsx
@@ -18,6 +18,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="2">
+    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00;\-#,##0.00;&quot;-&quot;"/>
+  </numFmts>
   <fonts count="40">
     <font>
       <name val="Calibri"/>
@@ -1997,28 +2001,28 @@
     <xf numFmtId="166" fontId="20" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="20" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="21" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="20" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="20" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="4" fontId="39" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">

--- a/public/plantilla-residuos.xlsx
+++ b/public/plantilla-residuos.xlsx
@@ -2946,7 +2946,7 @@
     <col width="20" customWidth="1" style="127" min="5" max="5"/>
     <col width="9" customWidth="1" style="127" min="6" max="6"/>
     <col width="8" customWidth="1" style="127" min="7" max="7"/>
-    <col width="16" customWidth="1" style="127" min="8" max="8"/>
+    <col width="20.78" customWidth="1" style="127" min="8" max="8"/>
     <col width="17" customWidth="1" style="127" min="9" max="9"/>
     <col width="21" customWidth="1" style="127" min="10" max="10"/>
     <col width="16" customWidth="1" style="127" min="11" max="11"/>

--- a/public/plantilla-residuos.xlsx
+++ b/public/plantilla-residuos.xlsx
@@ -8,9 +8,6 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Registro de Residuos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <externalReferences>
-    <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-  </externalReferences>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
 </workbook>
@@ -19,10 +16,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00;\-#,##0.00;&quot;-&quot;"/>
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00;\-#,##0.00;&quot;-&quot;"/>
   </numFmts>
-  <fonts count="40">
+  <fonts count="42">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -308,6 +305,15 @@
       <name val="Arial"/>
       <b val="1"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="23">
@@ -1054,7 +1060,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="383">
+  <cellXfs count="397">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
@@ -1977,13 +1983,13 @@
     <xf numFmtId="0" fontId="10" fillId="21" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="22" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -1998,7 +2004,7 @@
     <xf numFmtId="4" fontId="20" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="20" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -2027,6 +2033,55 @@
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="40" fillId="0" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="40" fillId="0" borderId="14" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="14" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="4" fontId="40" fillId="0" borderId="14" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="14" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="41" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -2248,391 +2303,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Permisos de Trabajo"/>
-      <sheetName val="Requisitos por permiso"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="4">
-          <cell r="A4" t="str">
-            <v>TRABAJO EN CALIENTE</v>
-          </cell>
-          <cell r="B4" t="str">
-            <v>TRABAJO EN FRÍO</v>
-          </cell>
-          <cell r="C4" t="str">
-            <v>TRABAJO EN ESPACIOS CONFINADOS</v>
-          </cell>
-          <cell r="D4" t="str">
-            <v>TRABAJOS ELÉCTRICOS</v>
-          </cell>
-          <cell r="E4" t="str">
-            <v>TRABAJO EN ALTURAS</v>
-          </cell>
-          <cell r="F4" t="str">
-            <v>EXCAVACIONES</v>
-          </cell>
-          <cell r="G4" t="str">
-            <v>TRABAJO CON RADIACIÓN</v>
-          </cell>
-          <cell r="H4" t="str">
-            <v>SUSTANCIAS PELIGROSAS O QUÍMICAS</v>
-          </cell>
-          <cell r="I4" t="str">
-            <v>TRABAJO EN CONDICIONES EXTREMAS</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="A5" t="str">
-            <v>Área despejada de combustibles e inflamables (o protegidos con mantas ignífugas)</v>
-          </cell>
-          <cell r="B5" t="str">
-            <v>Alcance del trabajo definido y confirmado: no genera chispas ni calor</v>
-          </cell>
-          <cell r="C5" t="str">
-            <v>Espacio identificado, señalizado y con acceso controlado</v>
-          </cell>
-          <cell r="D5" t="str">
-            <v>Personal competente y autorizado para el trabajo eléctrico (RETIE)</v>
-          </cell>
-          <cell r="E5" t="str">
-            <v>Personal con certificación vigente en trabajo seguro en alturas y aptitud médica</v>
-          </cell>
-          <cell r="F5" t="str">
-            <v>Servicios enterrados localizados y señalizados (gas, energía, agua y datos)</v>
-          </cell>
-          <cell r="G5" t="str">
-            <v>Personal autorizado con licencia o autorización vigente para manejo de fuentes radiactivas</v>
-          </cell>
-          <cell r="H5" t="str">
-            <v>Hojas de datos de seguridad (SDS) disponibles y leídas por el personal</v>
-          </cell>
-          <cell r="I5" t="str">
-            <v>Condiciones evaluadas (temperatura, radiación UV, lluvia, viento, tormenta eléctrica y visibilidad)</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="A6" t="str">
-            <v>Extintor adecuado, cargado y a la mano</v>
-          </cell>
-          <cell r="B6" t="str">
-            <v>Herramientas y equipos antichispa o que no generan fuentes de ignición</v>
-          </cell>
-          <cell r="C6" t="str">
-            <v>Personal autorizado con capacitación y certificación en espacios confinados</v>
-          </cell>
-          <cell r="D6" t="str">
-            <v>Procedimiento de bloqueo y etiquetado (LOTO) aplicado</v>
-          </cell>
-          <cell r="E6" t="str">
-            <v>Coordinador de trabajo en alturas presente</v>
-          </cell>
-          <cell r="F6" t="str">
-            <v>Tipo de suelo evaluado y sistema de contención definido (talud o entibado)</v>
-          </cell>
-          <cell r="G6" t="str">
-            <v>Oficial de protección radiológica designado y presente</v>
-          </cell>
-          <cell r="H6" t="str">
-            <v>Sustancias rotuladas con el sistema globalmente armonizado (SGA)</v>
-          </cell>
-          <cell r="I6" t="str">
-            <v>Criterios para suspender el trabajo definidos y comunicados</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="A7" t="str">
-            <v>Vigía de fuego designado (permanece 30 minutos después de terminar)</v>
-          </cell>
-          <cell r="B7" t="str">
-            <v>Equipos eléctricos y neumáticos aptos para la clasificación del área</v>
-          </cell>
-          <cell r="C7" t="str">
-            <v>Energías y fluidos aislados, bloqueados y etiquetados (tuberías, equipos, electricidad)</v>
-          </cell>
-          <cell r="D7" t="str">
-            <v>Circuito abierto y desenergizado en el punto de corte</v>
-          </cell>
-          <cell r="E7" t="str">
-            <v>Procedimiento de trabajo en alturas y ATS socializados</v>
-          </cell>
-          <cell r="F7" t="str">
-            <v>Taludes o entibados construidos según el diseño</v>
-          </cell>
-          <cell r="G7" t="str">
-            <v>Dosímetros personales asignados y en uso</v>
-          </cell>
-          <cell r="H7" t="str">
-            <v>Cantidad limitada a la necesaria y en recipientes adecuados</v>
-          </cell>
-          <cell r="I7" t="str">
-            <v>Hidratación disponible y pausas programadas</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="A8" t="str">
-            <v>Mantas o pantallas ignífugas contra chispas y escoria</v>
-          </cell>
-          <cell r="B8" t="str">
-            <v>Medición de atmósfera inflamable (LEL) realizada en el sitio</v>
-          </cell>
-          <cell r="C8" t="str">
-            <v>Medición de gases previa y continua (oxígeno, explosividad, CO y H₂S)</v>
-          </cell>
-          <cell r="D8" t="str">
-            <v>Ausencia de tensión verificada con detector adecuado</v>
-          </cell>
-          <cell r="E8" t="str">
-            <v>Sistema de acceso seguro (andamio certificado, escalera o plataforma inspeccionada)</v>
-          </cell>
-          <cell r="F8" t="str">
-            <v>Material excavado y equipos retirados del borde (distancia segura)</v>
-          </cell>
-          <cell r="G8" t="str">
-            <v>Fuente radiactiva identificada, con su certificado y registro de inventario</v>
-          </cell>
-          <cell r="H8" t="str">
-            <v>Compatibilidad entre sustancias verificada</v>
-          </cell>
-          <cell r="I8" t="str">
-            <v>Sombra, refugio o zona de descanso disponible</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="A9" t="str">
-            <v>Equipos de soldadura u oxicorte inspeccionados (cables, mangueras, válvulas y antirretorno)</v>
-          </cell>
-          <cell r="B9" t="str">
-            <v>Equipo o línea despresurizada, drenada y purgada (si aplica)</v>
-          </cell>
-          <cell r="C9" t="str">
-            <v>Ventilación natural o forzada en funcionamiento</v>
-          </cell>
-          <cell r="D9" t="str">
-            <v>Puesta a tierra temporal instalada</v>
-          </cell>
-          <cell r="E9" t="str">
-            <v>Puntos de anclaje identificados y con la resistencia requerida</v>
-          </cell>
-          <cell r="F9" t="str">
-            <v>Zona delimitada, con barandas o cerramiento y señalización visible</v>
-          </cell>
-          <cell r="G9" t="str">
-            <v>Área controlada delimitada y señalizada, con barreras y distancia segura calculada</v>
-          </cell>
-          <cell r="H9" t="str">
-            <v>Ventilación adecuada en el área de trabajo</v>
-          </cell>
-          <cell r="I9" t="str">
-            <v>Ropa adecuada al clima y protección solar</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="A10" t="str">
-            <v>Cilindros asegurados en posición vertical, con capuchón y lejos de la fuente de calor</v>
-          </cell>
-          <cell r="B10" t="str">
-            <v>Energías aisladas, bloqueadas y etiquetadas (LOTO)</v>
-          </cell>
-          <cell r="C10" t="str">
-            <v>Vigía permanente en el exterior con registro de ingreso y salida</v>
-          </cell>
-          <cell r="D10" t="str">
-            <v>Zona de trabajo delimitada y señalizada</v>
-          </cell>
-          <cell r="E10" t="str">
-            <v>Arnés, eslingas, absorbedor de impacto y línea de vida inspeccionados</v>
-          </cell>
-          <cell r="F10" t="str">
-            <v>Accesos y salidas seguros (escaleras o rampas) cerca del personal</v>
-          </cell>
-          <cell r="G10" t="str">
-            <v>Monitor de radiación calibrado y operativo</v>
-          </cell>
-          <cell r="H10" t="str">
-            <v>EPP específico (respirador, guantes, gafas, delantal) según la SDS</v>
-          </cell>
-          <cell r="I10" t="str">
-            <v>Aclimatación del personal nuevo o que regresa</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="A11" t="str">
-            <v>Ventilación o extracción de humos y gases</v>
-          </cell>
-          <cell r="B11" t="str">
-            <v>Superficies calientes y fuentes de ignición cercanas controladas</v>
-          </cell>
-          <cell r="C11" t="str">
-            <v>Comunicación continua entre el vigía y las personas en el interior</v>
-          </cell>
-          <cell r="D11" t="str">
-            <v>Distancias de seguridad respetadas frente a partes energizadas</v>
-          </cell>
-          <cell r="E11" t="str">
-            <v>Barandas, cerramientos o redes de protección instalados</v>
-          </cell>
-          <cell r="F11" t="str">
-            <v>Control de agua, drenaje o bombeo implementado</v>
-          </cell>
-          <cell r="G11" t="str">
-            <v>Personal ajeno evacuado o avisado del horario de la tarea</v>
-          </cell>
-          <cell r="H11" t="str">
-            <v>Duchas y lavaojos de emergencia disponibles y cercanos</v>
-          </cell>
-          <cell r="I11" t="str">
-            <v>Monitoreo de síntomas (golpe de calor, hipotermia y fatiga)</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="A12" t="str">
-            <v>Aberturas, ductos y alcantarillas cercanas selladas o protegidas</v>
-          </cell>
-          <cell r="B12" t="str">
-            <v>Extintor adecuado, cargado y a la mano</v>
-          </cell>
-          <cell r="C12" t="str">
-            <v>Plan de rescate, equipo de rescate (trípode, malacate) y respiración disponibles</v>
-          </cell>
-          <cell r="D12" t="str">
-            <v>EPP dieléctrico en buen estado (casco, guantes, calzado y careta)</v>
-          </cell>
-          <cell r="E12" t="str">
-            <v>Área inferior demarcada y señalizada contra caída de objetos</v>
-          </cell>
-          <cell r="F12" t="str">
-            <v>Inspección previa por persona competente (cada turno o después de lluvia)</v>
-          </cell>
-          <cell r="G12" t="str">
-            <v>Transporte y almacenamiento seguros de la fuente</v>
-          </cell>
-          <cell r="H12" t="str">
-            <v>Kit de derrames y material absorbente disponible</v>
-          </cell>
-          <cell r="I12" t="str">
-            <v>Iluminación suficiente si el trabajo es nocturno</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="A13" t="str">
-            <v>Medición de atmósfera inflamable realizada si hay riesgo de gases o vapores</v>
-          </cell>
-          <cell r="B13" t="str">
-            <v>EPP adecuado (guantes, gafas, ropa antiestática)</v>
-          </cell>
-          <cell r="C13" t="str">
-            <v>Iluminación y equipos aptos para el ambiente (a prueba de explosión si aplica)</v>
-          </cell>
-          <cell r="D13" t="str">
-            <v>Herramientas y equipos aislados, inspeccionados y con protección diferencial</v>
-          </cell>
-          <cell r="E13" t="str">
-            <v>Plan de rescate y equipo de rescate disponibles; personal entrenado</v>
-          </cell>
-          <cell r="F13" t="str">
-            <v>Atmósfera verificada si hay sospecha de gases (excavaciones profundas)</v>
-          </cell>
-          <cell r="G13" t="str">
-            <v>Control de tiempo de exposición, distancia y blindaje</v>
-          </cell>
-          <cell r="H13" t="str">
-            <v>Fuentes de ignición controladas o eliminadas</v>
-          </cell>
-          <cell r="I13" t="str">
-            <v>Trabajo en parejas o con vigía</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="A14" t="str">
-            <v>EPP específicos (careta, guantes, peto, polainas) y ropa sin material inflamable</v>
-          </cell>
-          <cell r="B14" t="str">
-            <v>Área delimitada y señalizada</v>
-          </cell>
-          <cell r="C14" t="str">
-            <v>Limpieza, drenaje o inertización del espacio realizada</v>
-          </cell>
-          <cell r="D14" t="str">
-            <v>Condiciones climáticas evaluadas (lluvia, tormenta eléctrica)</v>
-          </cell>
-          <cell r="E14" t="str">
-            <v>Herramientas aseguradas contra caídas</v>
-          </cell>
-          <cell r="F14" t="str">
-            <v>Control de tránsito y de vibraciones cerca de la excavación</v>
-          </cell>
-          <cell r="G14" t="str">
-            <v>Registro de dosis y bitácora de operación al día</v>
-          </cell>
-          <cell r="H14" t="str">
-            <v>Personal capacitado en manejo de sustancias químicas y en el plan de emergencia</v>
-          </cell>
-          <cell r="I14" t="str">
-            <v>Primeros auxilios y medio de comunicación disponibles</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="A15" t="str">
-            <v>Revisión del área 30 minutos después de terminar el trabajo</v>
-          </cell>
-          <cell r="B15" t="str">
-            <v>Procedimiento de trabajo y ATS conocidos por todo el personal</v>
-          </cell>
-          <cell r="C15" t="str">
-            <v>EPP y ropa adecuados al riesgo</v>
-          </cell>
-          <cell r="D15" t="str">
-            <v>Coordinación con el operador de red o responsable del sistema eléctrico</v>
-          </cell>
-          <cell r="E15" t="str">
-            <v>Condiciones climáticas evaluadas (lluvia, viento fuerte, tormenta eléctrica)</v>
-          </cell>
-          <cell r="F15" t="str">
-            <v>Plan de rescate y equipo básico de emergencia disponibles</v>
-          </cell>
-          <cell r="G15" t="str">
-            <v>Aptitud médica del personal expuesto</v>
-          </cell>
-          <cell r="H15" t="str">
-            <v>Disposición de residuos peligrosos definida</v>
-          </cell>
-          <cell r="I15" t="str">
-            <v>Plan de evacuación o suspensión ante tormenta eléctrica</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="A16"/>
-          <cell r="B16" t="str">
-            <v>Plan de emergencia y medio de comunicación disponibles</v>
-          </cell>
-          <cell r="C16" t="str">
-            <v>Tiempo máximo de permanencia definido</v>
-          </cell>
-          <cell r="D16"/>
-          <cell r="E16" t="str">
-            <v>Comunicación entre quien trabaja y el coordinador o vigía</v>
-          </cell>
-          <cell r="F16" t="str">
-            <v>EPP completos y vigía cuando se requiera</v>
-          </cell>
-          <cell r="G16" t="str">
-            <v>Plan de emergencia radiológica y contactos disponibles</v>
-          </cell>
-          <cell r="H16"/>
-          <cell r="I16"/>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3109,23 +2779,23 @@
       </c>
       <c r="B11" s="93" t="n"/>
       <c r="C11" s="89" t="n"/>
-      <c r="D11" s="68" t="n"/>
-      <c r="E11" s="93" t="n"/>
-      <c r="F11" s="93" t="n"/>
-      <c r="G11" s="93" t="n"/>
-      <c r="H11" s="89" t="n"/>
+      <c r="D11" s="383" t="n"/>
+      <c r="E11" s="384" t="n"/>
+      <c r="F11" s="384" t="n"/>
+      <c r="G11" s="384" t="n"/>
+      <c r="H11" s="385" t="n"/>
       <c r="I11" s="365" t="inlineStr">
         <is>
           <t>Periodo</t>
         </is>
       </c>
-      <c r="J11" s="69" t="n"/>
+      <c r="J11" s="386" t="n"/>
       <c r="K11" s="365" t="inlineStr">
         <is>
           <t>Hoja N°</t>
         </is>
       </c>
-      <c r="L11" s="69" t="n"/>
+      <c r="L11" s="386" t="n"/>
     </row>
     <row r="12" ht="21" customHeight="1" s="127">
       <c r="A12" s="365" t="inlineStr">
@@ -3135,23 +2805,23 @@
       </c>
       <c r="B12" s="93" t="n"/>
       <c r="C12" s="89" t="n"/>
-      <c r="D12" s="68" t="n"/>
-      <c r="E12" s="93" t="n"/>
-      <c r="F12" s="93" t="n"/>
-      <c r="G12" s="93" t="n"/>
-      <c r="H12" s="89" t="n"/>
+      <c r="D12" s="383" t="n"/>
+      <c r="E12" s="384" t="n"/>
+      <c r="F12" s="384" t="n"/>
+      <c r="G12" s="384" t="n"/>
+      <c r="H12" s="385" t="n"/>
       <c r="I12" s="365" t="inlineStr">
         <is>
           <t>Desde</t>
         </is>
       </c>
-      <c r="J12" s="366" t="n"/>
+      <c r="J12" s="387" t="n"/>
       <c r="K12" s="365" t="inlineStr">
         <is>
           <t>Hasta</t>
         </is>
       </c>
-      <c r="L12" s="366" t="n"/>
+      <c r="L12" s="387" t="n"/>
     </row>
     <row r="13" ht="16.5" customHeight="1" s="127">
       <c r="A13" s="364" t="inlineStr">
@@ -3234,404 +2904,404 @@
       </c>
     </row>
     <row r="15" ht="20" customHeight="1" s="127">
-      <c r="A15" s="306" t="n">
+      <c r="A15" s="388" t="n">
         <v>1</v>
       </c>
-      <c r="B15" s="368" t="n"/>
-      <c r="C15" s="230" t="n"/>
-      <c r="D15" s="230" t="n"/>
-      <c r="E15" s="230" t="n"/>
-      <c r="F15" s="372" t="n"/>
-      <c r="G15" s="306" t="n"/>
-      <c r="H15" s="230" t="n"/>
-      <c r="I15" s="230" t="n"/>
-      <c r="J15" s="230" t="n"/>
-      <c r="K15" s="230" t="n"/>
-      <c r="L15" s="230" t="n"/>
+      <c r="B15" s="389" t="n"/>
+      <c r="C15" s="390" t="n"/>
+      <c r="D15" s="390" t="n"/>
+      <c r="E15" s="390" t="n"/>
+      <c r="F15" s="391" t="n"/>
+      <c r="G15" s="392" t="n"/>
+      <c r="H15" s="390" t="n"/>
+      <c r="I15" s="390" t="n"/>
+      <c r="J15" s="390" t="n"/>
+      <c r="K15" s="390" t="n"/>
+      <c r="L15" s="390" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1" s="127">
-      <c r="A16" s="306" t="n">
+      <c r="A16" s="388" t="n">
         <v>2</v>
       </c>
-      <c r="B16" s="368" t="n"/>
-      <c r="C16" s="230" t="n"/>
-      <c r="D16" s="230" t="n"/>
-      <c r="E16" s="230" t="n"/>
-      <c r="F16" s="372" t="n"/>
-      <c r="G16" s="306" t="n"/>
-      <c r="H16" s="230" t="n"/>
-      <c r="I16" s="230" t="n"/>
-      <c r="J16" s="230" t="n"/>
-      <c r="K16" s="230" t="n"/>
-      <c r="L16" s="230" t="n"/>
+      <c r="B16" s="389" t="n"/>
+      <c r="C16" s="390" t="n"/>
+      <c r="D16" s="390" t="n"/>
+      <c r="E16" s="390" t="n"/>
+      <c r="F16" s="391" t="n"/>
+      <c r="G16" s="392" t="n"/>
+      <c r="H16" s="390" t="n"/>
+      <c r="I16" s="390" t="n"/>
+      <c r="J16" s="390" t="n"/>
+      <c r="K16" s="390" t="n"/>
+      <c r="L16" s="390" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1" s="127">
-      <c r="A17" s="306" t="n">
+      <c r="A17" s="388" t="n">
         <v>3</v>
       </c>
-      <c r="B17" s="368" t="n"/>
-      <c r="C17" s="230" t="n"/>
-      <c r="D17" s="230" t="n"/>
-      <c r="E17" s="230" t="n"/>
-      <c r="F17" s="372" t="n"/>
-      <c r="G17" s="306" t="n"/>
-      <c r="H17" s="230" t="n"/>
-      <c r="I17" s="230" t="n"/>
-      <c r="J17" s="230" t="n"/>
-      <c r="K17" s="230" t="n"/>
-      <c r="L17" s="230" t="n"/>
+      <c r="B17" s="389" t="n"/>
+      <c r="C17" s="390" t="n"/>
+      <c r="D17" s="390" t="n"/>
+      <c r="E17" s="390" t="n"/>
+      <c r="F17" s="391" t="n"/>
+      <c r="G17" s="392" t="n"/>
+      <c r="H17" s="390" t="n"/>
+      <c r="I17" s="390" t="n"/>
+      <c r="J17" s="390" t="n"/>
+      <c r="K17" s="390" t="n"/>
+      <c r="L17" s="390" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1" s="127">
-      <c r="A18" s="306" t="n">
+      <c r="A18" s="388" t="n">
         <v>4</v>
       </c>
-      <c r="B18" s="368" t="n"/>
-      <c r="C18" s="230" t="n"/>
-      <c r="D18" s="230" t="n"/>
-      <c r="E18" s="230" t="n"/>
-      <c r="F18" s="372" t="n"/>
-      <c r="G18" s="306" t="n"/>
-      <c r="H18" s="230" t="n"/>
-      <c r="I18" s="230" t="n"/>
-      <c r="J18" s="230" t="n"/>
-      <c r="K18" s="230" t="n"/>
-      <c r="L18" s="230" t="n"/>
+      <c r="B18" s="389" t="n"/>
+      <c r="C18" s="390" t="n"/>
+      <c r="D18" s="390" t="n"/>
+      <c r="E18" s="390" t="n"/>
+      <c r="F18" s="391" t="n"/>
+      <c r="G18" s="392" t="n"/>
+      <c r="H18" s="390" t="n"/>
+      <c r="I18" s="390" t="n"/>
+      <c r="J18" s="390" t="n"/>
+      <c r="K18" s="390" t="n"/>
+      <c r="L18" s="390" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1" s="127">
-      <c r="A19" s="306" t="n">
+      <c r="A19" s="388" t="n">
         <v>5</v>
       </c>
-      <c r="B19" s="368" t="n"/>
-      <c r="C19" s="230" t="n"/>
-      <c r="D19" s="230" t="n"/>
-      <c r="E19" s="230" t="n"/>
-      <c r="F19" s="372" t="n"/>
-      <c r="G19" s="306" t="n"/>
-      <c r="H19" s="230" t="n"/>
-      <c r="I19" s="230" t="n"/>
-      <c r="J19" s="230" t="n"/>
-      <c r="K19" s="230" t="n"/>
-      <c r="L19" s="230" t="n"/>
+      <c r="B19" s="389" t="n"/>
+      <c r="C19" s="390" t="n"/>
+      <c r="D19" s="390" t="n"/>
+      <c r="E19" s="390" t="n"/>
+      <c r="F19" s="391" t="n"/>
+      <c r="G19" s="392" t="n"/>
+      <c r="H19" s="390" t="n"/>
+      <c r="I19" s="390" t="n"/>
+      <c r="J19" s="390" t="n"/>
+      <c r="K19" s="390" t="n"/>
+      <c r="L19" s="390" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1" s="127">
-      <c r="A20" s="306" t="n">
+      <c r="A20" s="388" t="n">
         <v>6</v>
       </c>
-      <c r="B20" s="368" t="n"/>
-      <c r="C20" s="230" t="n"/>
-      <c r="D20" s="230" t="n"/>
-      <c r="E20" s="230" t="n"/>
-      <c r="F20" s="372" t="n"/>
-      <c r="G20" s="306" t="n"/>
-      <c r="H20" s="230" t="n"/>
-      <c r="I20" s="230" t="n"/>
-      <c r="J20" s="230" t="n"/>
-      <c r="K20" s="230" t="n"/>
-      <c r="L20" s="230" t="n"/>
+      <c r="B20" s="389" t="n"/>
+      <c r="C20" s="390" t="n"/>
+      <c r="D20" s="390" t="n"/>
+      <c r="E20" s="390" t="n"/>
+      <c r="F20" s="391" t="n"/>
+      <c r="G20" s="392" t="n"/>
+      <c r="H20" s="390" t="n"/>
+      <c r="I20" s="390" t="n"/>
+      <c r="J20" s="390" t="n"/>
+      <c r="K20" s="390" t="n"/>
+      <c r="L20" s="390" t="n"/>
     </row>
     <row r="21" ht="20" customHeight="1" s="127">
-      <c r="A21" s="306" t="n">
+      <c r="A21" s="388" t="n">
         <v>7</v>
       </c>
-      <c r="B21" s="368" t="n"/>
-      <c r="C21" s="230" t="n"/>
-      <c r="D21" s="230" t="n"/>
-      <c r="E21" s="230" t="n"/>
-      <c r="F21" s="372" t="n"/>
-      <c r="G21" s="306" t="n"/>
-      <c r="H21" s="230" t="n"/>
-      <c r="I21" s="230" t="n"/>
-      <c r="J21" s="230" t="n"/>
-      <c r="K21" s="230" t="n"/>
-      <c r="L21" s="230" t="n"/>
+      <c r="B21" s="389" t="n"/>
+      <c r="C21" s="390" t="n"/>
+      <c r="D21" s="390" t="n"/>
+      <c r="E21" s="390" t="n"/>
+      <c r="F21" s="391" t="n"/>
+      <c r="G21" s="392" t="n"/>
+      <c r="H21" s="390" t="n"/>
+      <c r="I21" s="390" t="n"/>
+      <c r="J21" s="390" t="n"/>
+      <c r="K21" s="390" t="n"/>
+      <c r="L21" s="390" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1" s="127">
-      <c r="A22" s="306" t="n">
+      <c r="A22" s="388" t="n">
         <v>8</v>
       </c>
-      <c r="B22" s="368" t="n"/>
-      <c r="C22" s="230" t="n"/>
-      <c r="D22" s="230" t="n"/>
-      <c r="E22" s="230" t="n"/>
-      <c r="F22" s="372" t="n"/>
-      <c r="G22" s="306" t="n"/>
-      <c r="H22" s="230" t="n"/>
-      <c r="I22" s="230" t="n"/>
-      <c r="J22" s="230" t="n"/>
-      <c r="K22" s="230" t="n"/>
-      <c r="L22" s="230" t="n"/>
+      <c r="B22" s="389" t="n"/>
+      <c r="C22" s="390" t="n"/>
+      <c r="D22" s="390" t="n"/>
+      <c r="E22" s="390" t="n"/>
+      <c r="F22" s="391" t="n"/>
+      <c r="G22" s="392" t="n"/>
+      <c r="H22" s="390" t="n"/>
+      <c r="I22" s="390" t="n"/>
+      <c r="J22" s="390" t="n"/>
+      <c r="K22" s="390" t="n"/>
+      <c r="L22" s="390" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1" s="127">
-      <c r="A23" s="306" t="n">
+      <c r="A23" s="388" t="n">
         <v>9</v>
       </c>
-      <c r="B23" s="368" t="n"/>
-      <c r="C23" s="230" t="n"/>
-      <c r="D23" s="230" t="n"/>
-      <c r="E23" s="230" t="n"/>
-      <c r="F23" s="372" t="n"/>
-      <c r="G23" s="306" t="n"/>
-      <c r="H23" s="230" t="n"/>
-      <c r="I23" s="230" t="n"/>
-      <c r="J23" s="230" t="n"/>
-      <c r="K23" s="230" t="n"/>
-      <c r="L23" s="230" t="n"/>
+      <c r="B23" s="389" t="n"/>
+      <c r="C23" s="390" t="n"/>
+      <c r="D23" s="390" t="n"/>
+      <c r="E23" s="390" t="n"/>
+      <c r="F23" s="391" t="n"/>
+      <c r="G23" s="392" t="n"/>
+      <c r="H23" s="390" t="n"/>
+      <c r="I23" s="390" t="n"/>
+      <c r="J23" s="390" t="n"/>
+      <c r="K23" s="390" t="n"/>
+      <c r="L23" s="390" t="n"/>
     </row>
     <row r="24" ht="20" customHeight="1" s="127">
-      <c r="A24" s="306" t="n">
+      <c r="A24" s="388" t="n">
         <v>10</v>
       </c>
-      <c r="B24" s="368" t="n"/>
-      <c r="C24" s="230" t="n"/>
-      <c r="D24" s="230" t="n"/>
-      <c r="E24" s="230" t="n"/>
-      <c r="F24" s="372" t="n"/>
-      <c r="G24" s="306" t="n"/>
-      <c r="H24" s="230" t="n"/>
-      <c r="I24" s="230" t="n"/>
-      <c r="J24" s="230" t="n"/>
-      <c r="K24" s="230" t="n"/>
-      <c r="L24" s="230" t="n"/>
+      <c r="B24" s="389" t="n"/>
+      <c r="C24" s="390" t="n"/>
+      <c r="D24" s="390" t="n"/>
+      <c r="E24" s="390" t="n"/>
+      <c r="F24" s="391" t="n"/>
+      <c r="G24" s="392" t="n"/>
+      <c r="H24" s="390" t="n"/>
+      <c r="I24" s="390" t="n"/>
+      <c r="J24" s="390" t="n"/>
+      <c r="K24" s="390" t="n"/>
+      <c r="L24" s="390" t="n"/>
     </row>
     <row r="25" ht="20" customHeight="1" s="127">
-      <c r="A25" s="306" t="n">
+      <c r="A25" s="388" t="n">
         <v>11</v>
       </c>
-      <c r="B25" s="368" t="n"/>
-      <c r="C25" s="230" t="n"/>
-      <c r="D25" s="230" t="n"/>
-      <c r="E25" s="230" t="n"/>
-      <c r="F25" s="372" t="n"/>
-      <c r="G25" s="306" t="n"/>
-      <c r="H25" s="230" t="n"/>
-      <c r="I25" s="230" t="n"/>
-      <c r="J25" s="230" t="n"/>
-      <c r="K25" s="230" t="n"/>
-      <c r="L25" s="230" t="n"/>
+      <c r="B25" s="389" t="n"/>
+      <c r="C25" s="390" t="n"/>
+      <c r="D25" s="390" t="n"/>
+      <c r="E25" s="390" t="n"/>
+      <c r="F25" s="391" t="n"/>
+      <c r="G25" s="392" t="n"/>
+      <c r="H25" s="390" t="n"/>
+      <c r="I25" s="390" t="n"/>
+      <c r="J25" s="390" t="n"/>
+      <c r="K25" s="390" t="n"/>
+      <c r="L25" s="390" t="n"/>
     </row>
     <row r="26" ht="20" customHeight="1" s="127">
-      <c r="A26" s="306" t="n">
+      <c r="A26" s="388" t="n">
         <v>12</v>
       </c>
-      <c r="B26" s="368" t="n"/>
-      <c r="C26" s="230" t="n"/>
-      <c r="D26" s="230" t="n"/>
-      <c r="E26" s="230" t="n"/>
-      <c r="F26" s="372" t="n"/>
-      <c r="G26" s="306" t="n"/>
-      <c r="H26" s="230" t="n"/>
-      <c r="I26" s="230" t="n"/>
-      <c r="J26" s="230" t="n"/>
-      <c r="K26" s="230" t="n"/>
-      <c r="L26" s="230" t="n"/>
+      <c r="B26" s="389" t="n"/>
+      <c r="C26" s="390" t="n"/>
+      <c r="D26" s="390" t="n"/>
+      <c r="E26" s="390" t="n"/>
+      <c r="F26" s="391" t="n"/>
+      <c r="G26" s="392" t="n"/>
+      <c r="H26" s="390" t="n"/>
+      <c r="I26" s="390" t="n"/>
+      <c r="J26" s="390" t="n"/>
+      <c r="K26" s="390" t="n"/>
+      <c r="L26" s="390" t="n"/>
     </row>
     <row r="27" ht="20" customHeight="1" s="127">
-      <c r="A27" s="306" t="n">
+      <c r="A27" s="388" t="n">
         <v>13</v>
       </c>
-      <c r="B27" s="368" t="n"/>
-      <c r="C27" s="230" t="n"/>
-      <c r="D27" s="230" t="n"/>
-      <c r="E27" s="230" t="n"/>
-      <c r="F27" s="372" t="n"/>
-      <c r="G27" s="306" t="n"/>
-      <c r="H27" s="230" t="n"/>
-      <c r="I27" s="230" t="n"/>
-      <c r="J27" s="230" t="n"/>
-      <c r="K27" s="230" t="n"/>
-      <c r="L27" s="230" t="n"/>
+      <c r="B27" s="389" t="n"/>
+      <c r="C27" s="390" t="n"/>
+      <c r="D27" s="390" t="n"/>
+      <c r="E27" s="390" t="n"/>
+      <c r="F27" s="391" t="n"/>
+      <c r="G27" s="392" t="n"/>
+      <c r="H27" s="390" t="n"/>
+      <c r="I27" s="390" t="n"/>
+      <c r="J27" s="390" t="n"/>
+      <c r="K27" s="390" t="n"/>
+      <c r="L27" s="390" t="n"/>
     </row>
     <row r="28" ht="20" customHeight="1" s="127">
-      <c r="A28" s="306" t="n">
+      <c r="A28" s="388" t="n">
         <v>14</v>
       </c>
-      <c r="B28" s="368" t="n"/>
-      <c r="C28" s="230" t="n"/>
-      <c r="D28" s="230" t="n"/>
-      <c r="E28" s="230" t="n"/>
-      <c r="F28" s="372" t="n"/>
-      <c r="G28" s="306" t="n"/>
-      <c r="H28" s="230" t="n"/>
-      <c r="I28" s="230" t="n"/>
-      <c r="J28" s="230" t="n"/>
-      <c r="K28" s="230" t="n"/>
-      <c r="L28" s="230" t="n"/>
+      <c r="B28" s="389" t="n"/>
+      <c r="C28" s="390" t="n"/>
+      <c r="D28" s="390" t="n"/>
+      <c r="E28" s="390" t="n"/>
+      <c r="F28" s="391" t="n"/>
+      <c r="G28" s="392" t="n"/>
+      <c r="H28" s="390" t="n"/>
+      <c r="I28" s="390" t="n"/>
+      <c r="J28" s="390" t="n"/>
+      <c r="K28" s="390" t="n"/>
+      <c r="L28" s="390" t="n"/>
     </row>
     <row r="29" ht="20" customHeight="1" s="127">
-      <c r="A29" s="306" t="n">
+      <c r="A29" s="388" t="n">
         <v>15</v>
       </c>
-      <c r="B29" s="368" t="n"/>
-      <c r="C29" s="230" t="n"/>
-      <c r="D29" s="230" t="n"/>
-      <c r="E29" s="230" t="n"/>
-      <c r="F29" s="372" t="n"/>
-      <c r="G29" s="306" t="n"/>
-      <c r="H29" s="230" t="n"/>
-      <c r="I29" s="230" t="n"/>
-      <c r="J29" s="230" t="n"/>
-      <c r="K29" s="230" t="n"/>
-      <c r="L29" s="230" t="n"/>
+      <c r="B29" s="389" t="n"/>
+      <c r="C29" s="390" t="n"/>
+      <c r="D29" s="390" t="n"/>
+      <c r="E29" s="390" t="n"/>
+      <c r="F29" s="391" t="n"/>
+      <c r="G29" s="392" t="n"/>
+      <c r="H29" s="390" t="n"/>
+      <c r="I29" s="390" t="n"/>
+      <c r="J29" s="390" t="n"/>
+      <c r="K29" s="390" t="n"/>
+      <c r="L29" s="390" t="n"/>
     </row>
     <row r="30" ht="20" customHeight="1" s="127">
-      <c r="A30" s="306" t="n">
+      <c r="A30" s="388" t="n">
         <v>16</v>
       </c>
-      <c r="B30" s="368" t="n"/>
-      <c r="C30" s="230" t="n"/>
-      <c r="D30" s="230" t="n"/>
-      <c r="E30" s="230" t="n"/>
-      <c r="F30" s="372" t="n"/>
-      <c r="G30" s="306" t="n"/>
-      <c r="H30" s="230" t="n"/>
-      <c r="I30" s="230" t="n"/>
-      <c r="J30" s="230" t="n"/>
-      <c r="K30" s="230" t="n"/>
-      <c r="L30" s="230" t="n"/>
+      <c r="B30" s="389" t="n"/>
+      <c r="C30" s="390" t="n"/>
+      <c r="D30" s="390" t="n"/>
+      <c r="E30" s="390" t="n"/>
+      <c r="F30" s="391" t="n"/>
+      <c r="G30" s="392" t="n"/>
+      <c r="H30" s="390" t="n"/>
+      <c r="I30" s="390" t="n"/>
+      <c r="J30" s="390" t="n"/>
+      <c r="K30" s="390" t="n"/>
+      <c r="L30" s="390" t="n"/>
     </row>
     <row r="31" ht="20" customHeight="1" s="127">
-      <c r="A31" s="306" t="n">
+      <c r="A31" s="388" t="n">
         <v>17</v>
       </c>
-      <c r="B31" s="368" t="n"/>
-      <c r="C31" s="230" t="n"/>
-      <c r="D31" s="230" t="n"/>
-      <c r="E31" s="230" t="n"/>
-      <c r="F31" s="372" t="n"/>
-      <c r="G31" s="306" t="n"/>
-      <c r="H31" s="230" t="n"/>
-      <c r="I31" s="230" t="n"/>
-      <c r="J31" s="230" t="n"/>
-      <c r="K31" s="230" t="n"/>
-      <c r="L31" s="230" t="n"/>
+      <c r="B31" s="389" t="n"/>
+      <c r="C31" s="390" t="n"/>
+      <c r="D31" s="390" t="n"/>
+      <c r="E31" s="390" t="n"/>
+      <c r="F31" s="391" t="n"/>
+      <c r="G31" s="392" t="n"/>
+      <c r="H31" s="390" t="n"/>
+      <c r="I31" s="390" t="n"/>
+      <c r="J31" s="390" t="n"/>
+      <c r="K31" s="390" t="n"/>
+      <c r="L31" s="390" t="n"/>
     </row>
     <row r="32" ht="20" customHeight="1" s="127">
-      <c r="A32" s="306" t="n">
+      <c r="A32" s="388" t="n">
         <v>18</v>
       </c>
-      <c r="B32" s="368" t="n"/>
-      <c r="C32" s="230" t="n"/>
-      <c r="D32" s="230" t="n"/>
-      <c r="E32" s="230" t="n"/>
-      <c r="F32" s="372" t="n"/>
-      <c r="G32" s="306" t="n"/>
-      <c r="H32" s="230" t="n"/>
-      <c r="I32" s="230" t="n"/>
-      <c r="J32" s="230" t="n"/>
-      <c r="K32" s="230" t="n"/>
-      <c r="L32" s="230" t="n"/>
+      <c r="B32" s="389" t="n"/>
+      <c r="C32" s="390" t="n"/>
+      <c r="D32" s="390" t="n"/>
+      <c r="E32" s="390" t="n"/>
+      <c r="F32" s="391" t="n"/>
+      <c r="G32" s="392" t="n"/>
+      <c r="H32" s="390" t="n"/>
+      <c r="I32" s="390" t="n"/>
+      <c r="J32" s="390" t="n"/>
+      <c r="K32" s="390" t="n"/>
+      <c r="L32" s="390" t="n"/>
     </row>
     <row r="33" ht="20" customHeight="1" s="127">
-      <c r="A33" s="306" t="n">
+      <c r="A33" s="388" t="n">
         <v>19</v>
       </c>
-      <c r="B33" s="368" t="n"/>
-      <c r="C33" s="230" t="n"/>
-      <c r="D33" s="230" t="n"/>
-      <c r="E33" s="230" t="n"/>
-      <c r="F33" s="372" t="n"/>
-      <c r="G33" s="306" t="n"/>
-      <c r="H33" s="230" t="n"/>
-      <c r="I33" s="230" t="n"/>
-      <c r="J33" s="230" t="n"/>
-      <c r="K33" s="230" t="n"/>
-      <c r="L33" s="230" t="n"/>
+      <c r="B33" s="389" t="n"/>
+      <c r="C33" s="390" t="n"/>
+      <c r="D33" s="390" t="n"/>
+      <c r="E33" s="390" t="n"/>
+      <c r="F33" s="391" t="n"/>
+      <c r="G33" s="392" t="n"/>
+      <c r="H33" s="390" t="n"/>
+      <c r="I33" s="390" t="n"/>
+      <c r="J33" s="390" t="n"/>
+      <c r="K33" s="390" t="n"/>
+      <c r="L33" s="390" t="n"/>
     </row>
     <row r="34" ht="20" customHeight="1" s="127">
-      <c r="A34" s="306" t="n">
+      <c r="A34" s="388" t="n">
         <v>20</v>
       </c>
-      <c r="B34" s="368" t="n"/>
-      <c r="C34" s="230" t="n"/>
-      <c r="D34" s="230" t="n"/>
-      <c r="E34" s="230" t="n"/>
-      <c r="F34" s="372" t="n"/>
-      <c r="G34" s="306" t="n"/>
-      <c r="H34" s="230" t="n"/>
-      <c r="I34" s="230" t="n"/>
-      <c r="J34" s="230" t="n"/>
-      <c r="K34" s="230" t="n"/>
-      <c r="L34" s="230" t="n"/>
+      <c r="B34" s="389" t="n"/>
+      <c r="C34" s="390" t="n"/>
+      <c r="D34" s="390" t="n"/>
+      <c r="E34" s="390" t="n"/>
+      <c r="F34" s="391" t="n"/>
+      <c r="G34" s="392" t="n"/>
+      <c r="H34" s="390" t="n"/>
+      <c r="I34" s="390" t="n"/>
+      <c r="J34" s="390" t="n"/>
+      <c r="K34" s="390" t="n"/>
+      <c r="L34" s="390" t="n"/>
     </row>
     <row r="35" ht="20" customHeight="1" s="127">
-      <c r="A35" s="306" t="n">
+      <c r="A35" s="388" t="n">
         <v>21</v>
       </c>
-      <c r="B35" s="368" t="n"/>
-      <c r="C35" s="230" t="n"/>
-      <c r="D35" s="230" t="n"/>
-      <c r="E35" s="230" t="n"/>
-      <c r="F35" s="372" t="n"/>
-      <c r="G35" s="306" t="n"/>
-      <c r="H35" s="230" t="n"/>
-      <c r="I35" s="230" t="n"/>
-      <c r="J35" s="230" t="n"/>
-      <c r="K35" s="230" t="n"/>
-      <c r="L35" s="230" t="n"/>
+      <c r="B35" s="389" t="n"/>
+      <c r="C35" s="390" t="n"/>
+      <c r="D35" s="390" t="n"/>
+      <c r="E35" s="390" t="n"/>
+      <c r="F35" s="391" t="n"/>
+      <c r="G35" s="392" t="n"/>
+      <c r="H35" s="390" t="n"/>
+      <c r="I35" s="390" t="n"/>
+      <c r="J35" s="390" t="n"/>
+      <c r="K35" s="390" t="n"/>
+      <c r="L35" s="390" t="n"/>
     </row>
     <row r="36" ht="20" customHeight="1" s="127">
-      <c r="A36" s="306" t="n">
+      <c r="A36" s="388" t="n">
         <v>22</v>
       </c>
-      <c r="B36" s="368" t="n"/>
-      <c r="C36" s="230" t="n"/>
-      <c r="D36" s="230" t="n"/>
-      <c r="E36" s="230" t="n"/>
-      <c r="F36" s="372" t="n"/>
-      <c r="G36" s="306" t="n"/>
-      <c r="H36" s="230" t="n"/>
-      <c r="I36" s="230" t="n"/>
-      <c r="J36" s="230" t="n"/>
-      <c r="K36" s="230" t="n"/>
-      <c r="L36" s="230" t="n"/>
+      <c r="B36" s="389" t="n"/>
+      <c r="C36" s="390" t="n"/>
+      <c r="D36" s="390" t="n"/>
+      <c r="E36" s="390" t="n"/>
+      <c r="F36" s="391" t="n"/>
+      <c r="G36" s="392" t="n"/>
+      <c r="H36" s="390" t="n"/>
+      <c r="I36" s="390" t="n"/>
+      <c r="J36" s="390" t="n"/>
+      <c r="K36" s="390" t="n"/>
+      <c r="L36" s="390" t="n"/>
     </row>
     <row r="37" ht="20" customHeight="1" s="127">
-      <c r="A37" s="306" t="n">
+      <c r="A37" s="388" t="n">
         <v>23</v>
       </c>
-      <c r="B37" s="368" t="n"/>
-      <c r="C37" s="230" t="n"/>
-      <c r="D37" s="230" t="n"/>
-      <c r="E37" s="230" t="n"/>
-      <c r="F37" s="372" t="n"/>
-      <c r="G37" s="306" t="n"/>
-      <c r="H37" s="230" t="n"/>
-      <c r="I37" s="230" t="n"/>
-      <c r="J37" s="230" t="n"/>
-      <c r="K37" s="230" t="n"/>
-      <c r="L37" s="230" t="n"/>
+      <c r="B37" s="389" t="n"/>
+      <c r="C37" s="390" t="n"/>
+      <c r="D37" s="390" t="n"/>
+      <c r="E37" s="390" t="n"/>
+      <c r="F37" s="391" t="n"/>
+      <c r="G37" s="392" t="n"/>
+      <c r="H37" s="390" t="n"/>
+      <c r="I37" s="390" t="n"/>
+      <c r="J37" s="390" t="n"/>
+      <c r="K37" s="390" t="n"/>
+      <c r="L37" s="390" t="n"/>
     </row>
     <row r="38" ht="20" customHeight="1" s="127">
-      <c r="A38" s="306" t="n">
+      <c r="A38" s="388" t="n">
         <v>24</v>
       </c>
-      <c r="B38" s="368" t="n"/>
-      <c r="C38" s="230" t="n"/>
-      <c r="D38" s="230" t="n"/>
-      <c r="E38" s="230" t="n"/>
-      <c r="F38" s="372" t="n"/>
-      <c r="G38" s="306" t="n"/>
-      <c r="H38" s="230" t="n"/>
-      <c r="I38" s="230" t="n"/>
-      <c r="J38" s="230" t="n"/>
-      <c r="K38" s="230" t="n"/>
-      <c r="L38" s="230" t="n"/>
+      <c r="B38" s="389" t="n"/>
+      <c r="C38" s="390" t="n"/>
+      <c r="D38" s="390" t="n"/>
+      <c r="E38" s="390" t="n"/>
+      <c r="F38" s="391" t="n"/>
+      <c r="G38" s="392" t="n"/>
+      <c r="H38" s="390" t="n"/>
+      <c r="I38" s="390" t="n"/>
+      <c r="J38" s="390" t="n"/>
+      <c r="K38" s="390" t="n"/>
+      <c r="L38" s="390" t="n"/>
     </row>
     <row r="39" ht="20" customHeight="1" s="127">
-      <c r="A39" s="306" t="n">
+      <c r="A39" s="388" t="n">
         <v>25</v>
       </c>
-      <c r="B39" s="368" t="n"/>
-      <c r="C39" s="230" t="n"/>
-      <c r="D39" s="230" t="n"/>
-      <c r="E39" s="230" t="n"/>
-      <c r="F39" s="372" t="n"/>
-      <c r="G39" s="306" t="n"/>
-      <c r="H39" s="230" t="n"/>
-      <c r="I39" s="230" t="n"/>
-      <c r="J39" s="230" t="n"/>
-      <c r="K39" s="230" t="n"/>
-      <c r="L39" s="230" t="n"/>
+      <c r="B39" s="389" t="n"/>
+      <c r="C39" s="390" t="n"/>
+      <c r="D39" s="390" t="n"/>
+      <c r="E39" s="390" t="n"/>
+      <c r="F39" s="391" t="n"/>
+      <c r="G39" s="392" t="n"/>
+      <c r="H39" s="390" t="n"/>
+      <c r="I39" s="390" t="n"/>
+      <c r="J39" s="390" t="n"/>
+      <c r="K39" s="390" t="n"/>
+      <c r="L39" s="390" t="n"/>
     </row>
     <row r="40" ht="16.5" customHeight="1" s="127">
       <c r="A40" s="364" t="inlineStr">
@@ -3694,202 +3364,202 @@
       <c r="L41" s="348" t="n"/>
     </row>
     <row r="42" ht="20" customHeight="1" s="127">
-      <c r="A42" s="230" t="inlineStr">
+      <c r="A42" s="393" t="inlineStr">
         <is>
           <t>RCD (escombros)</t>
         </is>
       </c>
       <c r="B42" s="98" t="n"/>
       <c r="C42" s="97" t="n"/>
-      <c r="D42" s="373">
+      <c r="D42" s="394">
         <f>SUMIFS($F$15:$F$39,$C$15:$C$39,$A42,$G$15:$G$39,"m³")</f>
         <v/>
       </c>
-      <c r="E42" s="373">
+      <c r="E42" s="394">
         <f>SUMIFS($F$15:$F$39,$C$15:$C$39,$A42,$G$15:$G$39,"kg")</f>
         <v/>
       </c>
-      <c r="F42" s="373">
+      <c r="F42" s="394">
         <f>SUMIFS($F$15:$F$39,$C$15:$C$39,$A42,$G$15:$G$39,"t")</f>
         <v/>
       </c>
       <c r="G42" s="97" t="n"/>
-      <c r="H42" s="373">
+      <c r="H42" s="394">
         <f>SUMIFS($F$15:$F$39,$C$15:$C$39,$A42,$G$15:$G$39,"gal")</f>
         <v/>
       </c>
-      <c r="I42" s="373">
+      <c r="I42" s="394">
         <f>SUMIFS($F$15:$F$39,$C$15:$C$39,$A42,$G$15:$G$39,"und")</f>
         <v/>
       </c>
-      <c r="J42" s="230" t="n"/>
-      <c r="K42" s="98" t="n"/>
-      <c r="L42" s="97" t="n"/>
+      <c r="J42" s="390" t="n"/>
+      <c r="K42" s="395" t="n"/>
+      <c r="L42" s="396" t="n"/>
     </row>
     <row r="43" ht="20" customHeight="1" s="127">
-      <c r="A43" s="230" t="inlineStr">
+      <c r="A43" s="393" t="inlineStr">
         <is>
           <t>Aprovechable</t>
         </is>
       </c>
       <c r="B43" s="98" t="n"/>
       <c r="C43" s="97" t="n"/>
-      <c r="D43" s="373">
+      <c r="D43" s="394">
         <f>SUMIFS($F$15:$F$39,$C$15:$C$39,$A43,$G$15:$G$39,"m³")</f>
         <v/>
       </c>
-      <c r="E43" s="373">
+      <c r="E43" s="394">
         <f>SUMIFS($F$15:$F$39,$C$15:$C$39,$A43,$G$15:$G$39,"kg")</f>
         <v/>
       </c>
-      <c r="F43" s="373">
+      <c r="F43" s="394">
         <f>SUMIFS($F$15:$F$39,$C$15:$C$39,$A43,$G$15:$G$39,"t")</f>
         <v/>
       </c>
       <c r="G43" s="97" t="n"/>
-      <c r="H43" s="373">
+      <c r="H43" s="394">
         <f>SUMIFS($F$15:$F$39,$C$15:$C$39,$A43,$G$15:$G$39,"gal")</f>
         <v/>
       </c>
-      <c r="I43" s="373">
+      <c r="I43" s="394">
         <f>SUMIFS($F$15:$F$39,$C$15:$C$39,$A43,$G$15:$G$39,"und")</f>
         <v/>
       </c>
-      <c r="J43" s="230" t="n"/>
-      <c r="K43" s="98" t="n"/>
-      <c r="L43" s="97" t="n"/>
+      <c r="J43" s="390" t="n"/>
+      <c r="K43" s="395" t="n"/>
+      <c r="L43" s="396" t="n"/>
     </row>
     <row r="44" ht="20" customHeight="1" s="127">
-      <c r="A44" s="230" t="inlineStr">
+      <c r="A44" s="393" t="inlineStr">
         <is>
           <t>Ordinario</t>
         </is>
       </c>
       <c r="B44" s="98" t="n"/>
       <c r="C44" s="97" t="n"/>
-      <c r="D44" s="373">
+      <c r="D44" s="394">
         <f>SUMIFS($F$15:$F$39,$C$15:$C$39,$A44,$G$15:$G$39,"m³")</f>
         <v/>
       </c>
-      <c r="E44" s="373">
+      <c r="E44" s="394">
         <f>SUMIFS($F$15:$F$39,$C$15:$C$39,$A44,$G$15:$G$39,"kg")</f>
         <v/>
       </c>
-      <c r="F44" s="373">
+      <c r="F44" s="394">
         <f>SUMIFS($F$15:$F$39,$C$15:$C$39,$A44,$G$15:$G$39,"t")</f>
         <v/>
       </c>
       <c r="G44" s="97" t="n"/>
-      <c r="H44" s="373">
+      <c r="H44" s="394">
         <f>SUMIFS($F$15:$F$39,$C$15:$C$39,$A44,$G$15:$G$39,"gal")</f>
         <v/>
       </c>
-      <c r="I44" s="373">
+      <c r="I44" s="394">
         <f>SUMIFS($F$15:$F$39,$C$15:$C$39,$A44,$G$15:$G$39,"und")</f>
         <v/>
       </c>
-      <c r="J44" s="230" t="n"/>
-      <c r="K44" s="98" t="n"/>
-      <c r="L44" s="97" t="n"/>
+      <c r="J44" s="390" t="n"/>
+      <c r="K44" s="395" t="n"/>
+      <c r="L44" s="396" t="n"/>
     </row>
     <row r="45" ht="20" customHeight="1" s="127">
-      <c r="A45" s="230" t="inlineStr">
+      <c r="A45" s="393" t="inlineStr">
         <is>
           <t>Orgánico / vegetal</t>
         </is>
       </c>
       <c r="B45" s="98" t="n"/>
       <c r="C45" s="97" t="n"/>
-      <c r="D45" s="373">
+      <c r="D45" s="394">
         <f>SUMIFS($F$15:$F$39,$C$15:$C$39,$A45,$G$15:$G$39,"m³")</f>
         <v/>
       </c>
-      <c r="E45" s="373">
+      <c r="E45" s="394">
         <f>SUMIFS($F$15:$F$39,$C$15:$C$39,$A45,$G$15:$G$39,"kg")</f>
         <v/>
       </c>
-      <c r="F45" s="373">
+      <c r="F45" s="394">
         <f>SUMIFS($F$15:$F$39,$C$15:$C$39,$A45,$G$15:$G$39,"t")</f>
         <v/>
       </c>
       <c r="G45" s="97" t="n"/>
-      <c r="H45" s="373">
+      <c r="H45" s="394">
         <f>SUMIFS($F$15:$F$39,$C$15:$C$39,$A45,$G$15:$G$39,"gal")</f>
         <v/>
       </c>
-      <c r="I45" s="373">
+      <c r="I45" s="394">
         <f>SUMIFS($F$15:$F$39,$C$15:$C$39,$A45,$G$15:$G$39,"und")</f>
         <v/>
       </c>
-      <c r="J45" s="230" t="n"/>
-      <c r="K45" s="98" t="n"/>
-      <c r="L45" s="97" t="n"/>
+      <c r="J45" s="390" t="n"/>
+      <c r="K45" s="395" t="n"/>
+      <c r="L45" s="396" t="n"/>
     </row>
     <row r="46" ht="20" customHeight="1" s="127">
-      <c r="A46" s="230" t="inlineStr">
+      <c r="A46" s="393" t="inlineStr">
         <is>
           <t>Peligroso (RESPEL)</t>
         </is>
       </c>
       <c r="B46" s="98" t="n"/>
       <c r="C46" s="97" t="n"/>
-      <c r="D46" s="373">
+      <c r="D46" s="394">
         <f>SUMIFS($F$15:$F$39,$C$15:$C$39,$A46,$G$15:$G$39,"m³")</f>
         <v/>
       </c>
-      <c r="E46" s="373">
+      <c r="E46" s="394">
         <f>SUMIFS($F$15:$F$39,$C$15:$C$39,$A46,$G$15:$G$39,"kg")</f>
         <v/>
       </c>
-      <c r="F46" s="373">
+      <c r="F46" s="394">
         <f>SUMIFS($F$15:$F$39,$C$15:$C$39,$A46,$G$15:$G$39,"t")</f>
         <v/>
       </c>
       <c r="G46" s="97" t="n"/>
-      <c r="H46" s="373">
+      <c r="H46" s="394">
         <f>SUMIFS($F$15:$F$39,$C$15:$C$39,$A46,$G$15:$G$39,"gal")</f>
         <v/>
       </c>
-      <c r="I46" s="373">
+      <c r="I46" s="394">
         <f>SUMIFS($F$15:$F$39,$C$15:$C$39,$A46,$G$15:$G$39,"und")</f>
         <v/>
       </c>
-      <c r="J46" s="230" t="n"/>
-      <c r="K46" s="98" t="n"/>
-      <c r="L46" s="97" t="n"/>
+      <c r="J46" s="390" t="n"/>
+      <c r="K46" s="395" t="n"/>
+      <c r="L46" s="396" t="n"/>
     </row>
     <row r="47" ht="20" customHeight="1" s="127">
-      <c r="A47" s="230" t="inlineStr">
+      <c r="A47" s="393" t="inlineStr">
         <is>
           <t>Especial / aceites usados</t>
         </is>
       </c>
       <c r="B47" s="98" t="n"/>
       <c r="C47" s="97" t="n"/>
-      <c r="D47" s="373">
+      <c r="D47" s="394">
         <f>SUMIFS($F$15:$F$39,$C$15:$C$39,$A47,$G$15:$G$39,"m³")</f>
         <v/>
       </c>
-      <c r="E47" s="373">
+      <c r="E47" s="394">
         <f>SUMIFS($F$15:$F$39,$C$15:$C$39,$A47,$G$15:$G$39,"kg")</f>
         <v/>
       </c>
-      <c r="F47" s="373">
+      <c r="F47" s="394">
         <f>SUMIFS($F$15:$F$39,$C$15:$C$39,$A47,$G$15:$G$39,"t")</f>
         <v/>
       </c>
       <c r="G47" s="97" t="n"/>
-      <c r="H47" s="373">
+      <c r="H47" s="394">
         <f>SUMIFS($F$15:$F$39,$C$15:$C$39,$A47,$G$15:$G$39,"gal")</f>
         <v/>
       </c>
-      <c r="I47" s="373">
+      <c r="I47" s="394">
         <f>SUMIFS($F$15:$F$39,$C$15:$C$39,$A47,$G$15:$G$39,"und")</f>
         <v/>
       </c>
-      <c r="J47" s="230" t="n"/>
-      <c r="K47" s="98" t="n"/>
-      <c r="L47" s="97" t="n"/>
+      <c r="J47" s="390" t="n"/>
+      <c r="K47" s="395" t="n"/>
+      <c r="L47" s="396" t="n"/>
     </row>
     <row r="48" ht="16" customHeight="1" s="127">
       <c r="A48" s="369" t="inlineStr">
@@ -3960,24 +3630,24 @@
         </is>
       </c>
       <c r="B51" s="97" t="n"/>
-      <c r="C51" s="301" t="n"/>
-      <c r="D51" s="98" t="n"/>
-      <c r="E51" s="97" t="n"/>
+      <c r="C51" s="390" t="n"/>
+      <c r="D51" s="395" t="n"/>
+      <c r="E51" s="396" t="n"/>
       <c r="F51" s="371" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="G51" s="97" t="n"/>
-      <c r="H51" s="301" t="n"/>
-      <c r="I51" s="97" t="n"/>
+      <c r="H51" s="390" t="n"/>
+      <c r="I51" s="396" t="n"/>
       <c r="J51" s="371" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
-      <c r="K51" s="301" t="n"/>
-      <c r="L51" s="97" t="n"/>
+      <c r="K51" s="390" t="n"/>
+      <c r="L51" s="396" t="n"/>
     </row>
     <row r="52" ht="21" customHeight="1" s="127">
       <c r="A52" s="371" t="inlineStr">
@@ -3986,24 +3656,24 @@
         </is>
       </c>
       <c r="B52" s="97" t="n"/>
-      <c r="C52" s="301" t="n"/>
-      <c r="D52" s="98" t="n"/>
-      <c r="E52" s="97" t="n"/>
+      <c r="C52" s="390" t="n"/>
+      <c r="D52" s="395" t="n"/>
+      <c r="E52" s="396" t="n"/>
       <c r="F52" s="371" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
       </c>
       <c r="G52" s="97" t="n"/>
-      <c r="H52" s="301" t="n"/>
-      <c r="I52" s="97" t="n"/>
+      <c r="H52" s="390" t="n"/>
+      <c r="I52" s="396" t="n"/>
       <c r="J52" s="371" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
       </c>
-      <c r="K52" s="301" t="n"/>
-      <c r="L52" s="97" t="n"/>
+      <c r="K52" s="390" t="n"/>
+      <c r="L52" s="396" t="n"/>
     </row>
     <row r="53" ht="21" customHeight="1" s="127">
       <c r="A53" s="371" t="inlineStr">
@@ -4012,24 +3682,24 @@
         </is>
       </c>
       <c r="B53" s="97" t="n"/>
-      <c r="C53" s="301" t="n"/>
-      <c r="D53" s="98" t="n"/>
-      <c r="E53" s="97" t="n"/>
+      <c r="C53" s="390" t="n"/>
+      <c r="D53" s="395" t="n"/>
+      <c r="E53" s="396" t="n"/>
       <c r="F53" s="371" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
       </c>
       <c r="G53" s="97" t="n"/>
-      <c r="H53" s="301" t="n"/>
-      <c r="I53" s="97" t="n"/>
+      <c r="H53" s="390" t="n"/>
+      <c r="I53" s="396" t="n"/>
       <c r="J53" s="371" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
       </c>
-      <c r="K53" s="301" t="n"/>
-      <c r="L53" s="97" t="n"/>
+      <c r="K53" s="390" t="n"/>
+      <c r="L53" s="396" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="25" t="inlineStr">
@@ -4043,6 +3713,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="59">
     <mergeCell ref="H53:I53"/>
     <mergeCell ref="A41:C41"/>
